--- a/employment_forms/023_simple_job_application_form--employment_forms.xlsx
+++ b/employment_forms/023_simple_job_application_form--employment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Name 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>years_employed</t>
+          <t>years_employed_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>years-employed</t>
+          <t>Years Employed 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
